--- a/tests/fixtures/compare/v2/項目定義.xlsx
+++ b/tests/fixtures/compare/v2/項目定義.xlsx
@@ -525,7 +525,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>追加シートの内容</t>
+          <t>変更履歴の内容</t>
         </is>
       </c>
     </row>
